--- a/stories/arbres/TREE-SAN-035.xlsx
+++ b/stories/arbres/TREE-SAN-035.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Lina est avec maman, à la maison. Lina a envie de jouer. maman est là, tout près. On va apprendre : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina écoute maman. Lina entend les mots : goûter, petite portion, nommer le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le bac à sable. L'eau coule, tout petit bruit. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2598,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2709,6 +2767,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2934,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3033,6 +3101,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3268,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3357,6 +3435,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3602,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3681,6 +3769,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3873,6 +3966,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4135,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4199,6 +4302,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4361,6 +4469,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4523,6 +4636,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4685,6 +4803,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4847,6 +4970,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5009,6 +5137,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5201,6 +5334,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5503,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,6 +5670,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5689,6 +5837,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5851,6 +6004,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6013,6 +6171,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6175,6 +6338,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6199,7 +6367,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6337,6 +6505,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers le toboggan. Un vélo passe au loin. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6517,6 +6691,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -6685,6 +6864,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6875,6 +7059,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7037,6 +7226,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. Les chaussures font toc toc. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7229,6 +7423,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7393,6 +7592,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7555,6 +7759,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7717,6 +7926,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7879,6 +8093,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8041,6 +8260,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8203,6 +8427,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8365,6 +8594,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. La couverture est douce. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8557,6 +8791,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8721,6 +8960,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8883,6 +9127,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9045,6 +9294,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9207,6 +9461,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9369,6 +9628,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9531,6 +9795,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9693,6 +9962,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. On entend un oiseau. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9885,6 +10159,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10049,6 +10328,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10211,6 +10495,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10373,6 +10662,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10535,6 +10829,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10697,6 +10996,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10859,6 +11163,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10883,7 +11192,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Lina va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On se tait une seconde. maman dit : je suis là. On reste ensemble.</t>
+          <t>Lina va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11021,6 +11330,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Lina va vers les balançoires. La lumière est claire. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Lina se souvient : goûter, petite portion, nommer le goût. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. On se tait une seconde.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11201,6 +11516,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
     </row>
@@ -11369,6 +11689,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11559,6 +11884,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11721,6 +12051,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11913,6 +12248,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12077,6 +12417,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12239,6 +12584,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12401,6 +12751,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12563,6 +12918,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12725,6 +13085,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le vent est doux. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12887,6 +13252,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13049,6 +13419,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13241,6 +13616,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13405,6 +13785,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13567,6 +13952,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13729,6 +14119,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13891,6 +14286,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14053,6 +14453,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Le sol est un peu froid. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14215,6 +14620,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14377,6 +14787,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Lina a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14569,6 +14984,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14733,6 +15153,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Tom. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14895,6 +15320,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15057,6 +15487,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Léa. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15219,6 +15654,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15381,6 +15821,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Lina rejoint Sami. Une feuille tombe. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15543,6 +15988,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15561,7 +16011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15634,6 +16084,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-035.xlsx
+++ b/stories/arbres/TREE-SAN-035.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Lina est avec maman, à la maison. Lina a envie de jouer. maman est là, tout près. On va apprendre : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina écoute maman. Lina entend les mots : goûter, petite portion, nommer le goût.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Lina a choisi le ballon. La lumière est claire. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2605,6 +2617,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2772,6 +2785,7 @@
           <t>narrateur|Lina rejoint Tom. Les chaussures font toc toc. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2939,6 +2953,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3106,6 +3121,7 @@
           <t>narrateur|Lina rejoint Léa. La couverture est douce. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3273,6 +3289,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3440,6 +3457,7 @@
           <t>narrateur|Lina rejoint Sami. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le bac à sable, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3607,6 +3625,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3774,6 +3793,7 @@
           <t>narrateur|Lina a choisi le seau. Il y a des miettes sur la table. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3973,6 +3993,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4140,6 +4161,7 @@
           <t>narrateur|Lina rejoint Tom. La couverture est douce. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4307,6 +4329,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4474,6 +4497,7 @@
           <t>narrateur|Lina rejoint Léa. On entend un oiseau. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4641,6 +4665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4808,6 +4833,7 @@
           <t>narrateur|Lina rejoint Sami. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le bac à sable, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4975,6 +5001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5142,6 +5169,7 @@
           <t>narrateur|Lina a choisi le doudou. Un chat miaule une fois. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5341,6 +5369,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5508,6 +5537,7 @@
           <t>narrateur|Lina rejoint Tom. On entend un oiseau. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5675,6 +5705,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5842,6 +5873,7 @@
           <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6009,6 +6041,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6176,6 +6209,7 @@
           <t>narrateur|Lina rejoint Sami. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le bac à sable, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6343,6 +6377,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6511,6 +6546,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6698,6 +6734,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6869,6 +6906,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7064,6 +7102,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7231,6 +7270,7 @@
           <t>narrateur|Lina a choisi le ballon. Les chaussures font toc toc. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7430,6 +7470,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7597,6 +7638,7 @@
           <t>narrateur|Lina rejoint Tom. La couverture est douce. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7764,6 +7806,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7931,6 +7974,7 @@
           <t>narrateur|Lina rejoint Léa. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8098,6 +8142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8265,6 +8310,7 @@
           <t>narrateur|Lina rejoint Sami. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de le toboggan, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8432,6 +8478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8599,6 +8646,7 @@
           <t>narrateur|Lina a choisi le seau. La couverture est douce. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8798,6 +8846,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8965,6 +9014,7 @@
           <t>narrateur|Lina rejoint Tom. On entend un oiseau. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9132,6 +9182,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9299,6 +9350,7 @@
           <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9466,6 +9518,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9633,6 +9686,7 @@
           <t>narrateur|Lina rejoint Sami. Le vent est doux. On se tient la main. Cette fin-là est celle de le toboggan, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9800,6 +9854,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9967,6 +10022,7 @@
           <t>narrateur|Lina a choisi le doudou. On entend un oiseau. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10166,6 +10222,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10333,6 +10390,7 @@
           <t>narrateur|Lina rejoint Tom. Ça sent le pain chaud. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10500,6 +10558,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10667,6 +10726,7 @@
           <t>narrateur|Lina rejoint Léa. Le vent est doux. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10834,6 +10894,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11001,6 +11062,7 @@
           <t>narrateur|Lina rejoint Sami. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de le toboggan, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11168,6 +11230,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11336,6 +11399,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11523,6 +11587,7 @@
           <t>narrateur|Que fait-on ? Goûter un légume.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11694,6 +11759,7 @@
           <t>narrateur|Oui. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina respire. Lina retient : goûter, petite portion, nommer le goût. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11889,6 +11955,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12056,6 +12123,7 @@
           <t>narrateur|Lina a choisi le ballon. Ça sent le pain chaud. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12255,6 +12323,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12422,6 +12491,7 @@
           <t>narrateur|Lina rejoint Tom. On entend un oiseau. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12589,6 +12659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12756,6 +12827,7 @@
           <t>narrateur|Lina rejoint Léa. Ça sent le pain chaud. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12923,6 +12995,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13090,6 +13163,7 @@
           <t>narrateur|Lina rejoint Sami. Le vent est doux. On range un objet. Cette fin-là est celle de les balançoires, le ballon et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13257,6 +13331,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13424,6 +13499,7 @@
           <t>narrateur|Lina a choisi le seau. Le vent est doux. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13623,6 +13699,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13790,6 +13867,7 @@
           <t>narrateur|Lina rejoint Tom. Ça sent le pain chaud. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13957,6 +14035,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14124,6 +14203,7 @@
           <t>narrateur|Lina rejoint Léa. Le vent est doux. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14291,6 +14371,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14458,6 +14539,7 @@
           <t>narrateur|Lina rejoint Sami. Le sol est un peu froid. On range un objet. Cette fin-là est celle de les balançoires, le seau et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14625,6 +14707,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14792,6 +14875,7 @@
           <t>narrateur|Lina a choisi le doudou. Le sol est un peu froid. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina répète tout bas : goûter, petite portion, nommer le goût. On dit merci. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14991,6 +15075,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15158,6 +15243,7 @@
           <t>narrateur|Lina rejoint Tom. Le vent est doux. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Tom. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15325,6 +15411,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15492,6 +15579,7 @@
           <t>narrateur|Lina rejoint Léa. Le sol est un peu froid. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Léa. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15659,6 +15747,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15826,6 +15915,7 @@
           <t>narrateur|Lina rejoint Sami. Une feuille tombe. On range un objet. Cette fin-là est celle de les balançoires, le doudou et Sami. Lina a appris : Goûter un légume. Voici le geste : prendre une petite bouchée ; dire le goût à papa ou maman. Lina a entendu : goûter, petite portion, nommer le goût. Lina dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15993,6 +16083,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16011,7 +16102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16091,6 +16182,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16105,7 +16210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16292,6 +16397,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
